--- a/KPI_Formula.xlsx
+++ b/KPI_Formula.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\2TB_HDD\OPTIMIZATION WR\2026\Others data\FEG Data\4Gtemp_ForReport\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6F0261F-AF58-4D7A-B618-EC0EB6BEEDAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E504E8-C194-493B-9765-577C4C896FD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{DC985ADB-6D98-4E1B-AD5A-9C33AA57D432}"/>
   </bookViews>
@@ -45,9 +45,6 @@
     <t>[L.Thrp.Time.DL.RmvLastTTI]*{1000}</t>
   </si>
   <si>
-    <t>([L.Thrp.bits.DL]+[L.Thrp.bits.DL.SRB]+[L.Thrp.bits.UL]+[L.Thrp.bits.UL.SRB])/{1000}/{1024}/{1024}/{8}</t>
-  </si>
-  <si>
     <t>[L.Traffic.User.Avg]</t>
   </si>
   <si>
@@ -72,9 +69,6 @@
     <t>DL PRB Utilization,%</t>
   </si>
   <si>
-    <t>DL PRB Utilization_N/DL PRB Utilization_D</t>
-  </si>
-  <si>
     <t>KPI Name</t>
   </si>
   <si>
@@ -85,6 +79,12 @@
   </si>
   <si>
     <t>Maximum Number of User</t>
+  </si>
+  <si>
+    <t>(DL PRB Utilization_N/DL PRB Utilization_D)*{100}</t>
+  </si>
+  <si>
+    <t>([L.Thrp.bits.DL]+[L.Thrp.bits.UL])/{1024}/{1024}/{1024}/{8}</t>
   </si>
 </sst>
 </file>
@@ -473,18 +473,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -505,26 +505,26 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -532,7 +532,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -540,15 +540,15 @@
         <v>3</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/KPI_Formula.xlsx
+++ b/KPI_Formula.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\2TB_HDD\OPTIMIZATION WR\2026\Others data\FEG Data\4Gtemp_ForReport\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E504E8-C194-493B-9765-577C4C896FD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{026326AB-00D2-4B1E-BDA9-0EC89CBE87C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{DC985ADB-6D98-4E1B-AD5A-9C33AA57D432}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>DL User Throughput_N</t>
   </si>
@@ -85,6 +85,36 @@
   </si>
   <si>
     <t>([L.Thrp.bits.DL]+[L.Thrp.bits.UL])/{1024}/{1024}/{1024}/{8}</t>
+  </si>
+  <si>
+    <t>PCell Data Vol,GB</t>
+  </si>
+  <si>
+    <t>SCell Data Vol,GB</t>
+  </si>
+  <si>
+    <t>CA DL User Throughput_N</t>
+  </si>
+  <si>
+    <t>L.Thrp.bits.DL.CAUser</t>
+  </si>
+  <si>
+    <t>CA DL User Throughput_D</t>
+  </si>
+  <si>
+    <t>L.Thrp.Time.DL.CAUser</t>
+  </si>
+  <si>
+    <t>CA DL User Throughput</t>
+  </si>
+  <si>
+    <t>(CA DL User Throughput_N/CA DL User Throughput_D)/{1000}</t>
+  </si>
+  <si>
+    <t>([L.CA.Traffic.bits.DL.PCell]+[L.CA.Traffic.bits.UL.PCell])/{1024}/{1024}/{1024}/{8}</t>
+  </si>
+  <si>
+    <t>([L.CA.Traffic.bits.DL.SCell]+[L.CA.Traffic.bits.UL.SCell])//{1024}/{1024}/{1024}/{8}</t>
   </si>
 </sst>
 </file>
@@ -115,7 +145,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -123,31 +153,16 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FFE6E6E6"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -464,11 +479,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{637A92E0-1E96-4242-8A6B-3C9BF13188C2}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="86.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="69.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -519,11 +534,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -535,8 +550,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -544,11 +559,51 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
